--- a/artfynd/A 6180-2026 artfynd.xlsx
+++ b/artfynd/A 6180-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>131054129</v>
       </c>
       <c r="B4" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>131054159</v>
       </c>
       <c r="B5" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131054152</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131054148</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>131054160</v>
       </c>
       <c r="B8" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131054161</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>131054149</v>
       </c>
       <c r="B11" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6180-2026 artfynd.xlsx
+++ b/artfynd/A 6180-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>131054129</v>
       </c>
       <c r="B4" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>131054159</v>
       </c>
       <c r="B5" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131054152</v>
       </c>
       <c r="B6" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131054148</v>
       </c>
       <c r="B7" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>131054160</v>
       </c>
       <c r="B8" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131054161</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>131054149</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6180-2026 artfynd.xlsx
+++ b/artfynd/A 6180-2026 artfynd.xlsx
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53961957</v>
+        <v>131054149</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edeby, 0,7 km O-ut, Upl</t>
+          <t>Rävmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660331.934637921</v>
+        <v>660399</v>
       </c>
       <c r="R2" t="n">
-        <v>6661636.904649271</v>
+        <v>6661680</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,70 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53961956</v>
+        <v>131054152</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edeby, 0,7 km O-ut, Upl</t>
+          <t>Rävmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660381.8064506405</v>
+        <v>660473</v>
       </c>
       <c r="R3" t="n">
-        <v>6661676.074692328</v>
+        <v>6661613</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-05-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sumpskogsområde dikat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,48 +882,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131054129</v>
+        <v>131054160</v>
       </c>
       <c r="B4" t="n">
-        <v>92277</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660317</v>
+        <v>660306</v>
       </c>
       <c r="R4" t="n">
-        <v>6661560</v>
+        <v>6661795</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,14 +1001,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131054159</v>
+        <v>131054129</v>
       </c>
       <c r="B5" t="n">
-        <v>92277</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660304</v>
+        <v>660317</v>
       </c>
       <c r="R5" t="n">
-        <v>6661793</v>
+        <v>6661560</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131054152</v>
+        <v>131054159</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660473</v>
+        <v>660304</v>
       </c>
       <c r="R6" t="n">
-        <v>6661613</v>
+        <v>6661793</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sumpskogsområde dikat</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131054148</v>
+        <v>131054161</v>
       </c>
       <c r="B7" t="n">
-        <v>58047</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660338</v>
+        <v>660212</v>
       </c>
       <c r="R7" t="n">
-        <v>6661656</v>
+        <v>6661786</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131054160</v>
+        <v>131054128</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660306</v>
+        <v>660278</v>
       </c>
       <c r="R8" t="n">
-        <v>6661795</v>
+        <v>6661596</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131054161</v>
+        <v>131054148</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660212</v>
+        <v>660338</v>
       </c>
       <c r="R9" t="n">
-        <v>6661786</v>
+        <v>6661656</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1519,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,48 +1536,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131054128</v>
+        <v>53961956</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävmossen, Upl</t>
+          <t>Edeby, 0,7 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660278</v>
+        <v>660382</v>
       </c>
       <c r="R10" t="n">
-        <v>6661596</v>
+        <v>6661676</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,22 +1602,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2015-05-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2015-05-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,60 +1622,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131054149</v>
+        <v>53961957</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rävmossen, Upl</t>
+          <t>Edeby, 0,7 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>660399</v>
+        <v>660332</v>
       </c>
       <c r="R11" t="n">
-        <v>6661680</v>
+        <v>6661637</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,22 +1704,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2015-05-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2015-05-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,15 +1724,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
